--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:11:40+00:00</t>
+    <t>2026-01-26T07:03:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:03:23+00:00</t>
+    <t>2026-01-26T07:12:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:12:25+00:00</t>
+    <t>2026-01-26T07:23:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:23:42+00:00</t>
+    <t>2026-03-01T19:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:57:07+00:00</t>
+    <t>2026-03-10T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T09:54:59+00:00</t>
+    <t>2026-03-12T09:42:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T09:42:23+00:00</t>
+    <t>2026-03-15T19:53:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -10,12 +10,14 @@
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
     <sheet name="Include #2" r:id="rId6" sheetId="4"/>
+    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
+    <sheet name="Include #4" r:id="rId8" sheetId="6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -62,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T19:53:47+00:00</t>
+    <t>2026-03-24T19:35:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,6 +116,12 @@
   </si>
   <si>
     <t>https://elga.moped.at/CodeSystem/LKFAbrechnungsGruppeAndereCS</t>
+  </si>
+  <si>
+    <t>https://elga.moped.at/CodeSystem/LKFAmbulantePauschalGruppenCS</t>
+  </si>
+  <si>
+    <t>https://elga.moped.at/CodeSystem/LKFAmbulantenMELGruppenCS</t>
   </si>
 </sst>
 </file>
@@ -493,4 +501,84 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T19:35:33+00:00</t>
+    <t>2026-03-24T20:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T20:07:54+00:00</t>
+    <t>2026-03-29T08:30:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T08:30:46+00:00</t>
+    <t>2026-03-29T16:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T16:14:43+00:00</t>
+    <t>2026-04-07T06:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T06:39:12+00:00</t>
+    <t>2026-04-07T10:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:38:55+00:00</t>
+    <t>2026-04-07T11:10:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T11:10:24+00:00</t>
+    <t>2026-04-07T12:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T12:18:59+00:00</t>
+    <t>2026-04-07T19:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:20:35+00:00</t>
+    <t>2026-04-07T19:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:34:12+00:00</t>
+    <t>2026-04-08T06:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T06:34:39+00:00</t>
+    <t>2026-04-08T08:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T08:16:43+00:00</t>
+    <t>2026-04-17T10:34:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T10:34:11+00:00</t>
+    <t>2026-04-23T07:59:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T07:59:48+00:00</t>
+    <t>2026-04-29T07:12:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:12:28+00:00</t>
+    <t>2026-04-29T07:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:28:34+00:00</t>
+    <t>2026-04-29T09:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T09:14:27+00:00</t>
+    <t>2026-05-05T07:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T07:22:12+00:00</t>
+    <t>2026-05-15T07:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T07:39:15+00:00</t>
+    <t>2026-05-15T09:26:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-LKFAbrechnungsGruppeVS.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T09:26:31+00:00</t>
+    <t>2026-05-22T08:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
